--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67622_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67622_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8a71547d2e1e40ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R10c7b147c7dc4e89"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    566.6190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    544.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    624.8184</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    651.1020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    598.5348</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    570.3738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    512.1744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    435.2010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    452.0976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67622_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67622_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R10c7b147c7dc4e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5953c59d8e86456f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    743.0946</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.1404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    457.7298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    485.8908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    476.5038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    534.7032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    566.6190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.1404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    938.3442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1045.3560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    818.1906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1240.6056</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    793.7844</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    671.7534</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    500.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    512.1744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    705.5466</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    698.0370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    514.0518</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    560.9868</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    711.1788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    713.0562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    782.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    775.0104</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    699.9144</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    692.4048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    666.1212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    388.2660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    444.5880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    485.8908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    500.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    568.4964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    538.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    440.8332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    452.0976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    457.7298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    437.0784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    437.0784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    427.6914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    410.7948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    440.8332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    433.3236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    523.4388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    574.1286</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    707.4240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    773.1330</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    744.9720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    591.0252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
